--- a/dev/StructureDefinition-ph-core-task.xlsx
+++ b/dev/StructureDefinition-ph-core-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-task.xlsx
+++ b/dev/StructureDefinition-ph-core-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-task.xlsx
+++ b/dev/StructureDefinition-ph-core-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-task.xlsx
+++ b/dev/StructureDefinition-ph-core-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
